--- a/physician_forms/002_virtual_care_appointment_form--physician_forms.xlsx
+++ b/physician_forms/002_virtual_care_appointment_form--physician_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -537,12 +537,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -560,12 +560,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -583,12 +583,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -606,12 +606,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -629,12 +629,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 6</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -652,12 +652,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -675,12 +675,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -698,12 +698,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -721,12 +721,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -744,12 +744,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 12</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -790,12 +790,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -813,12 +813,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -836,12 +836,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -859,12 +859,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -882,12 +882,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -905,12 +905,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 18</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -928,12 +928,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 19</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -951,12 +951,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -974,12 +974,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -997,12 +997,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 22</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 23</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>string_25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>&lt;string&gt;</t>
+          <t>String 25</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
